--- a/output/hierarchy_validation_report.xlsx
+++ b/output/hierarchy_validation_report.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:E258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>PAHH-211</t>
+          <t>V-BV-22</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2 parents: 001, V-PAHH-211</t>
+          <t>2 parents: V-BV-2247, V-BV-2248</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>V-TAHH-213</t>
+          <t>V-BV-2244</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2 parents: KM-V-201, V-TAHH-214</t>
+          <t>2 parents: V-BV-2242, V-BV-2243</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>V-PI-211</t>
+          <t>V-TE-213</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2 parents: PIT-211, V-PIT-211</t>
+          <t>2 parents: V-TE-213, V-TW-213</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TIT-212</t>
+          <t>V-TW-213</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2 parents: V-TIT-212, V-V-201</t>
+          <t>2 parents: T-258A, V-TW-213</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PIT-212</t>
+          <t>I-004X</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2 parents: K-V-201, V-PIT-212</t>
+          <t>2 parents: 004, 004X</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>V-TIT</t>
+          <t>V-XV-203</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2 parents: V-TIT-213, V-TIT-214</t>
+          <t>2 parents: S-V-204, V-XV-203</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>V-TIT-213</t>
+          <t>V-EZSC-209</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2 parents: KM-V-201, TIT-213</t>
+          <t>2 parents: V-EZSC-209, V-EZSO-209</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1IN</t>
+          <t>V-TT-217A</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2 parents: V-BV-2247, V-BV-2248</t>
+          <t>2 parents: S-V-204, T-217A</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>V-BV-2244</t>
+          <t>T-217A</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2 parents: V-BV-2242, V-V-201</t>
+          <t>2 parents: S-V-204, V-TT-217A</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>V-TIT-212</t>
+          <t>HS-466B</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2 parents: E-V-201, TIT-212</t>
+          <t>2 parents: HS-1466B, S-HS-1466B</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>TE-212</t>
+          <t>201A</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2 parents: V-TE-212, V-TW-212</t>
+          <t>2 parents: 12IN-C06B-61440X, T-201A</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>TW-212</t>
+          <t>V-LIT-206</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2 parents: T-256, V-TW-212</t>
+          <t>2 parents: V-GV-XX003, V-LIT-206</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>TI-211</t>
+          <t>T-46A</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2 parents: V-TI-211, V-TW-211</t>
+          <t>2 parents: T-246A, V-GV-922</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -857,2000 +857,2000 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: PIT-212, V-PIT-212</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>V-XS-239</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>V-TE-213</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: KM-V-201, TE-213</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>V-XS-239</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>V-TW-213</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: KM-V-201, TW-213</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>V-XA-237</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: TIT-213, V-TIT-213</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>V-XA-237</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>TIT-213</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: V-TIT-213, V-TIT-214</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>V-XS-238</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>V-BV-2245</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: V-BV-2248, V-V-201</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>V-XS-238</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>I-004X</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: 004, 004X</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>2IN-GV-V273-11</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>XV-203</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: S-V-204, V-XV-203</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2IN-GV-V273-11</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>V-XV-203</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: S-V-204, XV-203</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2IN-GV-V273-11502X</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>TE-213</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: V-TE-213, V-TW-213</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2IN-GV-V273-11502X</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12IN-ETH-V012-61440X-PP</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: 12IN-ETH-VO12-61440X—PP, KM-V-201</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>V-PIT-211</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>V-EZT-209</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: E-V-201, ZT-209</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>V-PIT-211</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>EZSC-209</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: V-EZSC-209, V-EZSO-209</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>V-RV-208</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>V-EZSC-209</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: EZSC-209, K-V-201</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>V-RV-208</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>V-EZSO-209</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: EZSO-209, K-V-201</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>V-BV-2248</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>V-NRV-...</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: K-V-201, V-NRV</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>V-BV-2248</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>V-EY-209</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: EY-209, K-V-201</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>V-HS-214A</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>V-NRV-748</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: K-V-201, V-NRV</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>V-HS-214A</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>V-TT-217A</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: S-V-204, T-217A</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>V-TAHH-213</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>2IN,CSO</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: K-V-201, V-BV-2249</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>V-TAHH-213</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>V-BV-2249</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: 2IN,CSO, V-V-03</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>V-BV-1920</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: K-V-201, V-BV-761</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>V-NRV</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: K-V-201, V-NRV-748</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>V—NRV-748</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: K-V-201, V-NRV</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>T-217A</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: S-V-204, V-TT-217A</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>V-GV-914</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>HS-466B</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: HS-1466B, S-HS-1466B</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>V-GV-914</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>XS-261</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: HS-466B, V-XS-261</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>PIT-214</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>7-61440X</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: 2IN-ETH-V067—61440X, K-V-201</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>PIT-214</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>201A</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: 12IN-C06B-61440X, T-201A</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>V-GV-913</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>V-GV-903</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: V-GV-904, V-V-201</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>V-GV-913</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>V-LIT-206</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: LIT-206, V-V-201</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>V-GV-91</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>LIC-204</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: V-LIC-204, V-V-201</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>V-GV-91</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>V-GV-XX004</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: V-GV-XX003, V-V-201</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>V-GV-917</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>LY-206</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: V-LY-206, V-V-201</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>V-GV-917</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>10IN—ETH-V061</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2 parents: 10IN-ETH-V061-61440X, V-V-201</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the true physical parent; remove spurious containment.</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>V-TIT-213</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>V-XS-239</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>V-TIT-213</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>V-TAHH-213</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>V-PAHH-213</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>V-PIT-213</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>V-PAHH-213</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>V-TIT</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>V-HS-214B</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>V-TIT-213</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>V-HS-214B</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>V-PAHH-213</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>V-TAHH-212</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>V-TAHH-212</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>V-TIT-212</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>V-TIT-212</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>V-GV-915</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>V-GV-915</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>PIT-210</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>PIT-210</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>V-TIT-211</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>V-TIT-214</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>V-TE-213</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>V-TW-213</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>TIT-213</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>V-TIT-211</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>V-TAHH-214</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>TAHH-213</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>V-TAHH-214</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>V-ZX-209</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>V-ZX-209</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>V-ZLO-209</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>V-ZLO-209</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>ZLC-209</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>TE-213</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>TW-213</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>ZLC-209</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>V-RST-209</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>V-RST-209</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>I-009X</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>I-009X</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>V-BV-2243</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>V-BV-2243</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>4IN-ETH-V060-61440X</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>4IN-ETH-V060-61440X</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>XY-203</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>XY-203</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>T-258A</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>T-258B</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>T-258A</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>V-TIC-213</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>V-TIC-213</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>V-TI-213</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>12IN-ETH-V012-61440X-PP</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>12IN-ETH-VO12-61440X—PP</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>V-EZT-209</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>ZT-209</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>V-BV-2241</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>12IN-ETH-V012-C06B-61440X</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>T-255A</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>V-BV-2249</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>V-FZT-208</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>V-FZSC-208</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>V-FZSO-208</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>V-ZY-208</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>KM-V-201</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>V-V-03</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic Hierarchy</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>E-V-201</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>effective-parent chain forms a cycle</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>Break reciprocal CONTAINED_WITHIN; pick one direction.</t>
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>V-TI-213</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>2IN-GV-V273-11</t>
+          <t>008</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>2IN-GV-V273-11</t>
+          <t>008</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>2IN-GV-V273-11502X</t>
+          <t>6IN-ETH-V058-61440X-PP</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>2IN-GV-V273-11502X</t>
+          <t>6IN-ETH-V058-61440X-PP</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>V-HS-214A</t>
+          <t>12IN-ETH-V012-61440X-PP</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>V-HS-214A</t>
+          <t>12IN-ETH-V012-61440X-PP</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>12IN-ETH-VO12-61440X—PP</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>12IN-ETH-VO12-61440X—PP</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>V-GV-91</t>
+          <t>V-EZT-209</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>V-GV-91</t>
+          <t>V-EZT-209</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>10IN-GV-V272-11502X</t>
+          <t>V-EZSO-209</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -3152,419 +3152,419 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>Disconnected Subgraph</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>10IN-GV-V272-11502X</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>isolated detection — no pipe/equipment/signal edge</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>Verify detection; connect or reject as false positive.</t>
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>V-EZSO-209</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>Missing System</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>10IN-GV-V272-11502X</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>no process system resolved</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>Assign to a process system.</t>
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>V-ESDV-209</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>Missing Parent</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>V-HS-214B</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>no equipment parent and not attached to any process line</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>Manually assign parent equipment or system.</t>
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>V-ESDV-209</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>Missing System</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>V-HS-214B</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>no process system resolved</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>Assign to a process system.</t>
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>V-NRV-...</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>Missing Parent</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>I-009X</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>no equipment parent and not attached to any process line</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>Manually assign parent equipment or system.</t>
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>V-NRV-...</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>Missing System</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>I-009X</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>no process system resolved</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>Assign to a process system.</t>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>V-EY-209</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>Missing Parent</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>V-TIC-213</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>no equipment parent and not attached to any process line</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>Manually assign parent equipment or system.</t>
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>V-EY-209</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>Missing System</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>V-TIC-213</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>no process system resolved</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>Assign to a process system.</t>
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>V-NRV-748</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>Missing Parent</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>008</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>no equipment parent and not attached to any process line</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>Manually assign parent equipment or system.</t>
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>V-NRV-748</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>Missing System</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>008</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>no process system resolved</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>Assign to a process system.</t>
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>2IN-ETH-V057-61440X</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>Missing Parent</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>6IN-ETH-V058-61440X-PP</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>no equipment parent and not attached to any process line</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>Manually assign parent equipment or system.</t>
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>2IN-ETH-V057-61440X</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>Missing System</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>6IN-ETH-V058-61440X-PP</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>no process system resolved</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>Assign to a process system.</t>
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>10IN-600#</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>Missing Parent</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>V-ESDV-209</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>no equipment parent and not attached to any process line</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>Manually assign parent equipment or system.</t>
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>10IN-600#</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>Missing System</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>V-ESDV-209</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>no process system resolved</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>Assign to a process system.</t>
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>2IN-600#</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>Missing Parent</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>V-ESDV-209</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>no equipment parent and not attached to any process line</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>Manually assign parent equipment or system.</t>
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>2IN-600#</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Disconnected Subgraph</t>
+          <t>Missing Parent</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>V-ESDV-209</t>
+          <t>V-BV-2241</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>isolated detection — no pipe/equipment/signal edge</t>
+          <t>no equipment parent and not attached to any process line</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Verify detection; connect or reject as false positive.</t>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>V-ESDV-209</t>
+          <t>V-BV-2241</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>2IN-ETH-V057-61440X</t>
+          <t>V-FIT-207</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>2IN-ETH-V057-61440X</t>
+          <t>V-FIT-207</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>4IN-ETH-V061-61440X-PP</t>
+          <t>V-FE-224</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>4IN-ETH-V061-61440X-PP</t>
+          <t>V-FE-224</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>4IN-ETH-V059-61440X-PP</t>
+          <t>4IN-ETH-V061-61440X-PP</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>4IN-ETH-V059-61440X-PP</t>
+          <t>4IN-ETH-V061-61440X-PP</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>V-PI-212</t>
+          <t>4IN-ETH-V059-61440X-PP</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>V-PI-212</t>
+          <t>4IN-ETH-V059-61440X-PP</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>12°-ETH-VO06-C03B</t>
+          <t>V-PI-212</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>12°-ETH-VO06-C03B</t>
+          <t>V-PI-212</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>V-PIC-210A</t>
+          <t>T-204A</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>V-PIC-210A</t>
+          <t>T-204A</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>PIC-1466B</t>
+          <t>12IN-ETH-V012-C06B-61440X</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>PIC-1466B</t>
+          <t>12IN-ETH-V012-C06B-61440X</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>S-HS-1466B</t>
+          <t>T-255B</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>S-HS-1466B</t>
+          <t>T-255B</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>T-201C</t>
+          <t>V-BV-760</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>T-201C</t>
+          <t>V-BV-760</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>V-Y2-207</t>
+          <t>2IN,CSO</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>V-Y2-207</t>
+          <t>2IN,CSO</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>V-XS-270</t>
+          <t>T-255A</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>V-XS-270</t>
+          <t>T-255A</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>V-HS-205</t>
+          <t>V-BV-2249</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>V-HS-205</t>
+          <t>V-BV-2249</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>V-SC-201</t>
+          <t>V-BV-1918</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>V-SC-201</t>
+          <t>V-BV-1918</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Y2-207</t>
+          <t>V-NRV</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Y2-207</t>
+          <t>V-NRV</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>V-PIC-252A</t>
+          <t>V—NRV-748</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>V-PIC-252A</t>
+          <t>V—NRV-748</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>V-PIC-252B</t>
+          <t>1IN-C06B-61440X</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>V-PIC-252B</t>
+          <t>1IN-C06B-61440X</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>V-XS-262</t>
+          <t>PDI-201</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>V-XS-262</t>
+          <t>PDI-201</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>PIC-52B</t>
+          <t>V-FIC-207</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>PIC-52B</t>
+          <t>V-FIC-207</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>V-FY-208</t>
+          <t>V-PIC-210</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>V-FY-208</t>
+          <t>V-PIC-210</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>V-PIC-004A</t>
+          <t>S-Y1</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>V-PIC-004A</t>
+          <t>S-Y1</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>V-PIC-04A</t>
+          <t>V-PIC-210A</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>V-PIC-04A</t>
+          <t>V-PIC-210A</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>V-FZI-208</t>
+          <t>V-PIC-212</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>V-FZI-208</t>
+          <t>V-PIC-212</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>V-FZY-208</t>
+          <t>PIC-1466B</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>V-FZY-208</t>
+          <t>PIC-1466B</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>V-FV-208</t>
+          <t>S-HS-1466B</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>V-FV-208</t>
+          <t>S-HS-1466B</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>8IN-ETH-V066-61440X</t>
+          <t>2IN-ETH-V067—61440X</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>8IN-ETH-V066-61440X</t>
+          <t>2IN-ETH-V067—61440X</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>1°-D-V003-C01B</t>
+          <t>7-61440X</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>1°-D-V003-C01B</t>
+          <t>7-61440X</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>2IN-ETH-V018</t>
+          <t>V-BV-761</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -5042,95 +5042,95 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>Disconnected Subgraph</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>2IN-ETH-V018</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>isolated detection — no pipe/equipment/signal edge</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>Verify detection; connect or reject as false positive.</t>
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>V-BV-761</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>Missing System</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>2IN-ETH-V018</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>no process system resolved</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>Assign to a process system.</t>
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>T-201C</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>Disconnected Subgraph</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t>01/E-V-201A</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>isolated detection — no pipe/equipment/signal edge</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>Verify detection; connect or reject as false positive.</t>
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>T-201C</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>Duplicate Nodes</t>
+          <t>Missing Parent</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>V-TAHH-213</t>
+          <t>V-LIC-204</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -5140,51 +5140,51 @@
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>2 nodes share tag 'V-TAHH-213'</t>
+          <t>no equipment parent and not attached to any process line</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Merge duplicate detections (step5d dedup).</t>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>Duplicate Nodes</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>2 nodes share tag '004'</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>Merge duplicate detections (step5d dedup).</t>
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>V-LIC-204</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>Duplicate Nodes</t>
+          <t>Missing Parent</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>I-004X</t>
+          <t>V-GV-XX003</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -5194,91 +5194,2251 @@
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>2 nodes share tag 'I-004X'</t>
+          <t>no equipment parent and not attached to any process line</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Merge duplicate detections (step5d dedup).</t>
+          <t>Manually assign parent equipment or system.</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>Duplicate Nodes</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>V-ESDV-209</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>2 nodes share tag 'V-ESDV-209'</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr">
-        <is>
-          <t>Merge duplicate detections (step5d dedup).</t>
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>V-GV-XX003</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>12IN-ETH-V009-C06</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>12IN-ETH-V009-C06</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>LAHH-206</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>LAHH-206</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>Y1-206</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>Y1-206</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>V-Y2-207</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>V-Y2-207</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>V-XS-270</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>V-XS-270</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>V-HS-205</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>V-HS-205</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>V-SC-201</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>V-SC-201</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>V-GV-904</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>V-GV-904</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>V-LV-206</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>Disconnected Subgraph</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>V-LV-206</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>isolated detection — no pipe/equipment/signal edge</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>Verify detection; connect or reject as false positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>V-LV-206</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>V-LV-206</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>Disconnected Subgraph</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>V-LV-206</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>isolated detection — no pipe/equipment/signal edge</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>Verify detection; connect or reject as false positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>V-LV-206</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>V-LY-206</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>V-LY-206</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>V-206</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>V-206</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D202" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E202" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>V-GV-XX004</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>V-GV-XX004</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D204" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>V-XI-220</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>V-XI-220</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D206" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>V-PIC-252A</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>V-PIC-252A</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>V-PIC-252B</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>V-PIC-252B</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>V-XS-262</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>V-XS-262</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>PIC-52B</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>PIC-52B</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>V-GV-922</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>V-GV-922</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D216" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E216" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>V-FZT-208</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>V-FZT-208</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D218" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>V-FY-208</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>V-FY-208</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>V-PIC-004A</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>V-PIC-004A</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>V-PIC-04A</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>V-PIC-04A</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>1IN-D-V006-C06B</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>1IN-D-V006-C06B</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>V-GLV-523</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>V-GLV-523</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E228" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>V-FZI-208</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>V-FZI-208</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E230" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>V-ZLC-208</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>V-ZLC-208</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D232" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E232" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>V-ZLO-208</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>V-ZLO-208</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D234" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E234" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>V-FZSO-208</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>V-FZSO-208</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D236" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E236" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>V-FZY-208</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>V-FZY-208</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D238" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E238" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>V-ZY-208</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>V-ZY-208</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D240" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E240" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>V-ZY-208</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>V-ZY-208</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D242" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E242" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>10IN—ETH-V061</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>10IN—ETH-V061</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E244" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>10IN-ETH-V061-61440X</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>10IN-ETH-V061-61440X</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E246" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>V-FV-208</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>V-FV-208</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E248" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>8IN-ETH-V066-61440X</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>8IN-ETH-V066-61440X</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E250" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>Missing Parent</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>1°-D-V003-C01B</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>no equipment parent and not attached to any process line</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>Manually assign parent equipment or system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>Missing System</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>1°-D-V003-C01B</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D252" s="4" t="inlineStr">
+        <is>
+          <t>no process system resolved</t>
+        </is>
+      </c>
+      <c r="E252" s="4" t="inlineStr">
+        <is>
+          <t>Assign to a process system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
           <t>Duplicate Nodes</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>V-TAHH-213</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>2 nodes share tag 'V-TAHH-213'</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>Merge duplicate detections (step5d dedup).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate Nodes</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>2 nodes share tag '004'</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>Merge duplicate detections (step5d dedup).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate Nodes</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>I-004X</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>2 nodes share tag 'I-004X'</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>Merge duplicate detections (step5d dedup).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate Nodes</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>V-ESDV-209</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>2 nodes share tag 'V-ESDV-209'</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>Merge duplicate detections (step5d dedup).</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate Nodes</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
         <is>
           <t>V-LV-206</t>
         </is>
       </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
         <is>
           <t>2 nodes share tag 'V-LV-206'</t>
         </is>
       </c>
-      <c r="E177" s="3" t="inlineStr">
+      <c r="E257" s="3" t="inlineStr">
         <is>
           <t>Merge duplicate detections (step5d dedup).</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="3" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
         <is>
           <t>Duplicate Nodes</t>
         </is>
       </c>
-      <c r="B178" s="3" t="inlineStr">
+      <c r="B258" s="3" t="inlineStr">
         <is>
           <t>V-ZY-208</t>
         </is>
       </c>
-      <c r="C178" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D178" s="3" t="inlineStr">
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
         <is>
           <t>2 nodes share tag 'V-ZY-208'</t>
         </is>
       </c>
-      <c r="E178" s="3" t="inlineStr">
+      <c r="E258" s="3" t="inlineStr">
         <is>
           <t>Merge duplicate detections (step5d dedup).</t>
         </is>
@@ -5295,7 +7455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5321,7 +7481,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>177</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
@@ -5331,7 +7491,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>87</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -5341,7 +7501,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>40</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5">
@@ -5351,67 +7511,57 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>50</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Type: Cyclic Hierarchy</t>
+          <t>Type: Disconnected Subgraph</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Type: Disconnected Subgraph</t>
+          <t>Type: Duplicate Nodes</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Type: Duplicate Nodes</t>
+          <t>Type: Missing Parent</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>6</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Type: Missing Parent</t>
+          <t>Type: Missing System</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>40</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Type: Missing System</t>
+          <t>Type: Multiple Parents</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Type: Multiple Parents</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
